--- a/test-files/sheet-modifications/missing-sheet-output.xlsx
+++ b/test-files/sheet-modifications/missing-sheet-output.xlsx
@@ -1,16 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kitsuneh\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9972" firstSheet="10" activeTab="11"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
@@ -23,172 +14,45 @@
     <sheet name="network" sheetId="9" r:id="rId9"/>
     <sheet name="network_weights" sheetId="10" r:id="rId10"/>
     <sheet name="network_optimized_b" sheetId="11" r:id="rId11"/>
-    <sheet name="concentration_sigmas" sheetId="13" r:id="rId12"/>
+    <sheet name="concentration_sigmas" sheetId="12" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="49">
-  <si>
-    <t>SystematicName</t>
-  </si>
-  <si>
-    <t>StandardName</t>
-  </si>
-  <si>
-    <t>YKL112W</t>
-  </si>
-  <si>
-    <t>ABF1</t>
-  </si>
-  <si>
-    <t>YLR131C</t>
-  </si>
-  <si>
-    <t>ACE2</t>
-  </si>
-  <si>
-    <t>YGL071W</t>
-  </si>
-  <si>
-    <t>AFT1</t>
-  </si>
-  <si>
-    <t>YOR028C</t>
-  </si>
-  <si>
-    <t>CIN5</t>
-  </si>
-  <si>
-    <t>YPL177C</t>
-  </si>
-  <si>
-    <t>CUP9</t>
-  </si>
-  <si>
-    <t>YPR104C</t>
-  </si>
-  <si>
-    <t>FHL1</t>
-  </si>
-  <si>
-    <t>YGL181W</t>
-  </si>
-  <si>
-    <t>GTS1</t>
-  </si>
-  <si>
-    <t>YOL089C</t>
-  </si>
-  <si>
-    <t>HAL9</t>
-  </si>
-  <si>
-    <t>YGL073W</t>
-  </si>
-  <si>
-    <t>HSF1</t>
-  </si>
-  <si>
-    <t>YMR021C</t>
-  </si>
-  <si>
-    <t>MAC1</t>
-  </si>
-  <si>
-    <t>YOL116W</t>
-  </si>
-  <si>
-    <t>MSN1</t>
-  </si>
-  <si>
-    <t>YKL062W</t>
-  </si>
-  <si>
-    <t>MSN4</t>
-  </si>
-  <si>
-    <t>YDR043C</t>
-  </si>
-  <si>
-    <t>NRG1</t>
-  </si>
-  <si>
-    <t>YKL043W</t>
-  </si>
-  <si>
-    <t>PHD1</t>
-  </si>
-  <si>
-    <t>YNL216W</t>
-  </si>
-  <si>
-    <t>RAP1</t>
-  </si>
-  <si>
-    <t>YBR049C</t>
-  </si>
-  <si>
-    <t>REB1</t>
-  </si>
-  <si>
-    <t>YPR065W</t>
-  </si>
-  <si>
-    <t>ROX1</t>
-  </si>
-  <si>
-    <t>YER169W</t>
-  </si>
-  <si>
-    <t>RPH1</t>
-  </si>
-  <si>
-    <t>YHR206W</t>
-  </si>
-  <si>
-    <t>SKN7</t>
-  </si>
-  <si>
-    <t>YML007W</t>
-  </si>
-  <si>
-    <t>YAP1</t>
-  </si>
-  <si>
-    <t>YDR259C</t>
-  </si>
-  <si>
-    <t>YAP6</t>
-  </si>
-  <si>
-    <t>DegradationRate</t>
-  </si>
-  <si>
-    <t>production_rates</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>rows genes affected/cols genes controlling</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -212,21 +76,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -273,7 +129,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -308,7 +164,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -375,20 +231,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -510,96 +362,136 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>rows genes affected/cols genes controlling</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ABF1</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ACE2</v>
+      </c>
+      <c r="D1" t="str">
+        <v>AFT1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>CIN5</v>
+      </c>
+      <c r="F1" t="str">
+        <v>CUP9</v>
+      </c>
+      <c r="G1" t="str">
+        <v>FHL1</v>
+      </c>
+      <c r="H1" t="str">
+        <v>GTS1</v>
+      </c>
+      <c r="I1" t="str">
+        <v>HAL9</v>
+      </c>
+      <c r="J1" t="str">
+        <v>HSF1</v>
+      </c>
+      <c r="K1" t="str">
+        <v>MAC1</v>
+      </c>
+      <c r="L1" t="str">
+        <v>MSN1</v>
+      </c>
+      <c r="M1" t="str">
+        <v>MSN4</v>
+      </c>
+      <c r="N1" t="str">
+        <v>NRG1</v>
+      </c>
+      <c r="O1" t="str">
+        <v>PHD1</v>
+      </c>
+      <c r="P1" t="str">
+        <v>RAP1</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>REB1</v>
+      </c>
+      <c r="R1" t="str">
+        <v>ROX1</v>
+      </c>
+      <c r="S1" t="str">
+        <v>RPH1</v>
+      </c>
+      <c r="T1" t="str">
+        <v>SKN7</v>
+      </c>
+      <c r="U1" t="str">
+        <v>YAP1</v>
+      </c>
+      <c r="V1" t="str">
+        <v>YAP6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ABF1</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -665,9 +557,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ACE2</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -733,9 +625,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>AFT1</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -801,9 +693,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -869,9 +761,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CUP9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -937,9 +829,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FHL1</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1005,9 +897,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>15</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>GTS1</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1073,9 +965,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>17</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HAL9</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1141,9 +1033,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HSF1</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1209,9 +1101,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>21</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>MAC1</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1277,9 +1169,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>23</v>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>MSN1</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1345,9 +1237,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>25</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>MSN4</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1413,9 +1305,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>27</v>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>NRG1</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1481,9 +1373,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1549,9 +1441,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>RAP1</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1617,9 +1509,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>33</v>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>REB1</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1685,9 +1577,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>35</v>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ROX1</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1753,9 +1645,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>37</v>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>RPH1</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1821,9 +1713,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>39</v>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SKN7</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1889,9 +1781,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>41</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YAP1</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1957,9 +1849,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>43</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YAP6</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2027,272 +1919,276 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:V22"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>b</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YKL112W</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ABF1</v>
       </c>
       <c r="C2">
         <v>3.5832424503284495</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ACE2</v>
       </c>
       <c r="C3">
         <v>0.43639050107171085</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YGL071W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AFT1</v>
       </c>
       <c r="C4">
-        <v>0.92252832272777818</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+        <v>0.9225283227277782</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YPL177C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CUP9</v>
       </c>
       <c r="C6">
         <v>2.0910823308027027</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YPR104C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FHL1</v>
       </c>
       <c r="C7">
-        <v>0.70302987263964267</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>0.7030298726396427</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YGL181W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GTS1</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YOL089C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>HAL9</v>
       </c>
       <c r="C9">
         <v>1.705484132961856</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YGL073W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>HSF1</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YMR021C</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MAC1</v>
       </c>
       <c r="C11">
         <v>1.9790215778846847</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YOL116W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MSN1</v>
       </c>
       <c r="C12">
-        <v>0.60210848377180937</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+        <v>0.6021084837718094</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MSN4</v>
       </c>
       <c r="C13">
         <v>0.46995435034263766</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YDR043C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>NRG1</v>
       </c>
       <c r="C14">
         <v>1.8752370569606065</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL043W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="C15">
-        <v>0.39660977074993559</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
+        <v>0.3966097707499356</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YNL216W</v>
+      </c>
+      <c r="B16" t="str">
+        <v>RAP1</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YBR049C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>REB1</v>
       </c>
       <c r="C17">
         <v>-0.41004540733244454</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YPR065W</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ROX1</v>
       </c>
       <c r="C18">
-        <v>0.96462921382440314</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
+        <v>0.9646292138244031</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YER169W</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RPH1</v>
       </c>
       <c r="C19">
         <v>0.46922152532428346</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YHR206W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SKN7</v>
       </c>
       <c r="C20">
-        <v>2.0323815421584288</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
+        <v>2.032381542158429</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YML007W</v>
+      </c>
+      <c r="B21" t="str">
+        <v>YAP1</v>
       </c>
       <c r="C21">
-        <v>0.88883637179023933</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
+        <v>0.8888363717902393</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YDR259C</v>
+      </c>
+      <c r="B22" t="str">
+        <v>YAP6</v>
       </c>
       <c r="C22">
-        <v>2.3366106137446918</v>
+        <v>2.336610613744692</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
       </c>
       <c r="C1">
         <v>15</v>
@@ -2304,236 +2200,236 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YKL112W</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ABF1</v>
       </c>
       <c r="C2">
-        <v>0.91727409105065705</v>
+        <v>0.917274091050657</v>
       </c>
       <c r="D2">
-        <v>0.44210879486447602</v>
+        <v>0.442108794864476</v>
       </c>
       <c r="E2">
-        <v>0.69315515241602899</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+        <v>0.693155152416029</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ACE2</v>
       </c>
       <c r="C3">
-        <v>0.71685637353245302</v>
+        <v>0.716856373532453</v>
       </c>
       <c r="D3">
         <v>0.641384013885964</v>
       </c>
       <c r="E3">
-        <v>0.92245951116837099</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>0.922459511168371</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YGL071W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AFT1</v>
       </c>
       <c r="C4">
-        <v>0.44470247868505602</v>
+        <v>0.444702478685056</v>
       </c>
       <c r="D4">
-        <v>0.53164120946850402</v>
+        <v>0.531641209468504</v>
       </c>
       <c r="E4">
         <v>0.320493749001932</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="C5">
-        <v>0.81727687981679498</v>
+        <v>0.817276879816795</v>
       </c>
       <c r="D5">
-        <v>0.95726655288635398</v>
+        <v>0.957266552886354</v>
       </c>
       <c r="E5">
-        <v>0.70281582595053704</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+        <v>0.702815825950537</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YPL177C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CUP9</v>
       </c>
       <c r="C6">
-        <v>1.0967850406720701</v>
+        <v>1.09678504067207</v>
       </c>
       <c r="D6">
-        <v>0.52970920759899298</v>
+        <v>0.529709207598993</v>
       </c>
       <c r="E6">
-        <v>0.80891828959740097</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+        <v>0.808918289597401</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YPR104C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FHL1</v>
       </c>
       <c r="C7">
-        <v>0.42580145197082703</v>
+        <v>0.425801451970827</v>
       </c>
       <c r="D7">
-        <v>0.63499396842678302</v>
+        <v>0.634993968426783</v>
       </c>
       <c r="E7">
-        <v>0.78157727034137603</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>0.781577270341376</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YGL181W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GTS1</v>
       </c>
       <c r="C8">
         <v>0.404638632823907</v>
       </c>
       <c r="D8">
-        <v>0.58989131883839296</v>
+        <v>0.589891318838393</v>
       </c>
       <c r="E8">
-        <v>0.60748498565234699</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
+        <v>0.607484985652347</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YOL089C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>HAL9</v>
       </c>
       <c r="C9">
-        <v>0.68943520086600596</v>
+        <v>0.689435200866006</v>
       </c>
       <c r="D9">
-        <v>1.8955428214225301</v>
+        <v>1.89554282142253</v>
       </c>
       <c r="E9">
-        <v>0.54723644512184799</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+        <v>0.547236445121848</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YGL073W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>HSF1</v>
       </c>
       <c r="C10">
-        <v>0.97726406268218102</v>
+        <v>0.977264062682181</v>
       </c>
       <c r="D10">
-        <v>0.72420652572711597</v>
+        <v>0.724206525727116</v>
       </c>
       <c r="E10">
         <v>1.09985790153451</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YMR021C</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MAC1</v>
       </c>
       <c r="C11">
-        <v>0.72504670083612599</v>
+        <v>0.725046700836126</v>
       </c>
       <c r="D11">
-        <v>0.20779307950352699</v>
+        <v>0.207793079503527</v>
       </c>
       <c r="E11">
-        <v>0.65825511050072905</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
+        <v>0.658255110500729</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YOL116W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MSN1</v>
       </c>
       <c r="C12">
-        <v>0.51852196117730698</v>
+        <v>0.518521961177307</v>
       </c>
       <c r="D12">
-        <v>0.88709656674279203</v>
+        <v>0.887096566742792</v>
       </c>
       <c r="E12">
         <v>0.248881921070051</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MSN4</v>
       </c>
       <c r="C13">
-        <v>1.6409513470958299</v>
+        <v>1.64095134709583</v>
       </c>
       <c r="D13">
         <v>1.01226276719667</v>
       </c>
       <c r="E13">
-        <v>1.2436321609087699</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
+        <v>1.24363216090877</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YDR043C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>NRG1</v>
       </c>
       <c r="C14">
-        <v>0.56438763790471502</v>
+        <v>0.564387637904715</v>
       </c>
       <c r="D14">
         <v>0.637046148638169</v>
       </c>
       <c r="E14">
-        <v>0.76246682595887705</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
+        <v>0.762466825958877</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL043W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="C15">
-        <v>0.48729361226630702</v>
+        <v>0.487293612266307</v>
       </c>
       <c r="D15">
         <v>0.460208681767377</v>
@@ -2542,120 +2438,120 @@
         <v>0.389622153973187</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YNL216W</v>
+      </c>
+      <c r="B16" t="str">
+        <v>RAP1</v>
       </c>
       <c r="C16">
         <v>1.72099674768658</v>
       </c>
       <c r="D16">
-        <v>0.85831878781873805</v>
+        <v>0.858318787818738</v>
       </c>
       <c r="E16">
-        <v>0.44772738659776701</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>0.447727386597767</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YBR049C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>REB1</v>
       </c>
       <c r="C17">
-        <v>0.50452893050955805</v>
+        <v>0.504528930509558</v>
       </c>
       <c r="D17">
-        <v>0.75370009518917203</v>
+        <v>0.753700095189172</v>
       </c>
       <c r="E17">
         <v>1.07122097617887</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YPR065W</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ROX1</v>
       </c>
       <c r="C18">
-        <v>1.1966265259256601</v>
+        <v>1.19662652592566</v>
       </c>
       <c r="D18">
-        <v>1.1801382981458799</v>
+        <v>1.18013829814588</v>
       </c>
       <c r="E18">
-        <v>0.35000209622478101</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
+        <v>0.350002096224781</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YER169W</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RPH1</v>
       </c>
       <c r="C19">
         <v>1.48156426614991</v>
       </c>
       <c r="D19">
-        <v>1.7277862291131501</v>
+        <v>1.72778622911315</v>
       </c>
       <c r="E19">
-        <v>0.89902628670097295</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
+        <v>0.899026286700973</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YHR206W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SKN7</v>
       </c>
       <c r="C20">
         <v>1.10568541431009</v>
       </c>
       <c r="D20">
-        <v>0.84212726958299999</v>
+        <v>0.842127269583</v>
       </c>
       <c r="E20">
-        <v>0.74688657635395606</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
+        <v>0.746886576353956</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YML007W</v>
+      </c>
+      <c r="B21" t="str">
+        <v>YAP1</v>
       </c>
       <c r="C21">
-        <v>0.65898902973629203</v>
+        <v>0.658989029736292</v>
       </c>
       <c r="D21">
-        <v>0.43418451003840802</v>
+        <v>0.434184510038408</v>
       </c>
       <c r="E21">
-        <v>0.53794081650927705</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
+        <v>0.537940816509277</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YDR259C</v>
+      </c>
+      <c r="B22" t="str">
+        <v>YAP6</v>
       </c>
       <c r="C22">
-        <v>0.40923963868872798</v>
+        <v>0.409239638688728</v>
       </c>
       <c r="D22">
-        <v>0.28048461336490499</v>
+        <v>0.280484613364905</v>
       </c>
       <c r="E22">
         <v>0.287254982132019</v>
@@ -2663,38 +2559,44 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E22"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
       </c>
       <c r="C1">
         <v>15</v>
@@ -2706,29 +2608,29 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YKL112W</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ABF1</v>
       </c>
       <c r="C2">
-        <v>-1.1802129985963199</v>
+        <v>-1.18021299859632</v>
       </c>
       <c r="D2">
         <v>-1.35534786374789</v>
       </c>
       <c r="E2">
-        <v>-2.2843447109758301</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+        <v>-2.28434471097583</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ACE2</v>
       </c>
       <c r="C3">
         <v>-0.168317226797601</v>
@@ -2737,219 +2639,219 @@
         <v>0.159981381075125</v>
       </c>
       <c r="E3">
-        <v>-8.4072251269262696E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>-0.0840722512692627</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YGL071W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AFT1</v>
       </c>
       <c r="C4">
         <v>0.110916570402342</v>
       </c>
       <c r="D4">
-        <v>0.34518552113600498</v>
+        <v>0.345185521136005</v>
       </c>
       <c r="E4">
-        <v>0.29611171632314098</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+        <v>0.296111716323141</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="C5">
-        <v>0.57398886351082801</v>
+        <v>0.573988863510828</v>
       </c>
       <c r="D5">
-        <v>0.90044244474717405</v>
+        <v>0.900442444747174</v>
       </c>
       <c r="E5">
         <v>1.75845186354745</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YPL177C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CUP9</v>
       </c>
       <c r="C6">
-        <v>-0.34976006979129598</v>
+        <v>-0.349760069791296</v>
       </c>
       <c r="D6">
-        <v>-0.97753185452394098</v>
+        <v>-0.977531854523941</v>
       </c>
       <c r="E6">
-        <v>-0.76236366760055096</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+        <v>-0.762363667600551</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YPR104C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FHL1</v>
       </c>
       <c r="C7">
-        <v>-4.4276309137313001E-2</v>
+        <v>-0.044276309137313</v>
       </c>
       <c r="D7">
-        <v>0.24181613073483699</v>
+        <v>0.241816130734837</v>
       </c>
       <c r="E7">
-        <v>0.62853290835895503</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>0.628532908358955</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YGL181W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GTS1</v>
       </c>
       <c r="C8">
         <v>-0.220356822259166</v>
       </c>
       <c r="D8">
-        <v>-0.11669113002233999</v>
+        <v>-0.11669113002234</v>
       </c>
       <c r="E8">
-        <v>-8.7143718210927298E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
+        <v>-0.0871437182109273</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YOL089C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>HAL9</v>
       </c>
       <c r="C9">
-        <v>-0.16064769982257401</v>
+        <v>-0.160647699822574</v>
       </c>
       <c r="D9">
-        <v>0.20886614963405101</v>
+        <v>0.208866149634051</v>
       </c>
       <c r="E9">
-        <v>0.84698244904192099</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+        <v>0.846982449041921</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YGL073W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>HSF1</v>
       </c>
       <c r="C10">
-        <v>-0.97765022692802495</v>
+        <v>-0.977650226928025</v>
       </c>
       <c r="D10">
-        <v>-1.1044654053835501</v>
+        <v>-1.10446540538355</v>
       </c>
       <c r="E10">
-        <v>-0.73218305564943398</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
+        <v>-0.732183055649434</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YMR021C</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MAC1</v>
       </c>
       <c r="C11">
-        <v>0.61308674677972397</v>
+        <v>0.613086746779724</v>
       </c>
       <c r="D11">
-        <v>0.49022096483014099</v>
+        <v>0.490220964830141</v>
       </c>
       <c r="E11">
-        <v>0.45176478094112998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
+        <v>0.45176478094113</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YOL116W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MSN1</v>
       </c>
       <c r="C12">
         <v>0.124182913442922</v>
       </c>
       <c r="D12">
-        <v>-0.42545856172641699</v>
+        <v>-0.425458561726417</v>
       </c>
       <c r="E12">
-        <v>-0.48116619434522001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+        <v>-0.48116619434522</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MSN4</v>
       </c>
       <c r="C13">
-        <v>0.98300627566904297</v>
+        <v>0.983006275669043</v>
       </c>
       <c r="D13">
         <v>0.976858174028987</v>
       </c>
       <c r="E13">
-        <v>1.4416179829439899</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
+        <v>1.44161798294399</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YDR043C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>NRG1</v>
       </c>
       <c r="C14">
-        <v>-0.75199845082126104</v>
+        <v>-0.751998450821261</v>
       </c>
       <c r="D14">
-        <v>-0.39598482761536302</v>
+        <v>-0.395984827615363</v>
       </c>
       <c r="E14">
-        <v>-0.29043031142040199</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
+        <v>-0.290430311420402</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL043W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="C15">
-        <v>0.40478070501389601</v>
+        <v>0.404780705013896</v>
       </c>
       <c r="D15">
-        <v>0.63962144886654104</v>
+        <v>0.639621448866541</v>
       </c>
       <c r="E15">
-        <v>0.41039596022329999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
+        <v>0.4103959602233</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YNL216W</v>
+      </c>
+      <c r="B16" t="str">
+        <v>RAP1</v>
       </c>
       <c r="C16">
         <v>-1.41026384750747</v>
@@ -2958,32 +2860,32 @@
         <v>-0.269044364431755</v>
       </c>
       <c r="E16">
-        <v>9.0586658239791298E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>0.0905866582397913</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YBR049C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>REB1</v>
       </c>
       <c r="C17">
         <v>-0.105709302884452</v>
       </c>
       <c r="D17">
-        <v>-0.25108884778781598</v>
+        <v>-0.251088847787816</v>
       </c>
       <c r="E17">
-        <v>-0.19878651280399501</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+        <v>-0.198786512803995</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YPR065W</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ROX1</v>
       </c>
       <c r="C18">
         <v>-1.02661929129623</v>
@@ -2992,93 +2894,95 @@
         <v>-1.26262750699747</v>
       </c>
       <c r="E18">
-        <v>-1.1921015273515501</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
+        <v>-1.19210152735155</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YER169W</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RPH1</v>
       </c>
       <c r="C19">
-        <v>1.3177110283620199</v>
+        <v>1.31771102836202</v>
       </c>
       <c r="D19">
-        <v>1.2880472692047999</v>
+        <v>1.2880472692048</v>
       </c>
       <c r="E19">
-        <v>1.5309831587774501</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
+        <v>1.53098315877745</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YHR206W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SKN7</v>
       </c>
       <c r="C20">
-        <v>0.40820898095417801</v>
+        <v>0.408208980954178</v>
       </c>
       <c r="D20">
-        <v>1.0500276907448201</v>
+        <v>1.05002769074482</v>
       </c>
       <c r="E20">
-        <v>1.4171295501935499</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
+        <v>1.41712955019355</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YML007W</v>
+      </c>
+      <c r="B21" t="str">
+        <v>YAP1</v>
       </c>
       <c r="C21">
-        <v>1.4028761460241701</v>
+        <v>1.40287614602417</v>
       </c>
       <c r="D21">
-        <v>1.2314519660749701</v>
+        <v>1.23145196607497</v>
       </c>
       <c r="E21">
         <v>1.50806209670647</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YDR259C</v>
+      </c>
+      <c r="B22" t="str">
+        <v>YAP6</v>
       </c>
       <c r="C22">
-        <v>-0.66486605652808095</v>
+        <v>-0.664866056528081</v>
       </c>
       <c r="D22">
-        <v>-0.51022603008343204</v>
+        <v>-0.510226030083432</v>
       </c>
       <c r="E22">
-        <v>-0.72124064515279496</v>
+        <v>-0.721240645152795</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E22"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
       </c>
       <c r="C1">
         <v>0</v>
@@ -3102,12 +3006,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YKL112W</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ABF1</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -3131,41 +3035,41 @@
         <v>-2.0801205398917544</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ACE2</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>-5.6749260882462654E-2</v>
+        <v>-0.056749260882462654</v>
       </c>
       <c r="E3">
-        <v>-4.4552411545758612E-2</v>
+        <v>-0.04455241154575861</v>
       </c>
       <c r="F3">
-        <v>-3.0425317302871315E-2</v>
+        <v>-0.030425317302871315</v>
       </c>
       <c r="G3">
-        <v>-1.9980324833994145E-2</v>
+        <v>-0.019980324833994145</v>
       </c>
       <c r="H3">
-        <v>-1.2654342896178249E-2</v>
+        <v>-0.012654342896178249</v>
       </c>
       <c r="I3">
-        <v>-7.5661817313969412E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>-0.007566181731396941</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YGL071W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AFT1</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -3177,33 +3081,33 @@
         <v>0.20547164391680572</v>
       </c>
       <c r="F4">
-        <v>0.25888404359409278</v>
+        <v>0.2588840435940928</v>
       </c>
       <c r="G4">
         <v>0.29425243289460334</v>
       </c>
       <c r="H4">
-        <v>0.31752746475699478</v>
+        <v>0.3175274647569948</v>
       </c>
       <c r="I4">
         <v>0.33259896435719805</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0.59866935216683292</v>
+        <v>0.5986693521668329</v>
       </c>
       <c r="E5">
-        <v>0.93072512842680555</v>
+        <v>0.9307251284268055</v>
       </c>
       <c r="F5">
         <v>1.1406971744025163</v>
@@ -3218,12 +3122,12 @@
         <v>1.453115800515161</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YPL177C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CUP9</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -3235,24 +3139,24 @@
         <v>-0.46274780394210174</v>
       </c>
       <c r="F6">
-        <v>-0.64140659381398724</v>
+        <v>-0.6414065938139872</v>
       </c>
       <c r="G6">
-        <v>-0.78120517765525332</v>
+        <v>-0.7812051776552533</v>
       </c>
       <c r="H6">
-        <v>-0.88730821263249826</v>
+        <v>-0.8873082126324983</v>
       </c>
       <c r="I6">
-        <v>-0.96577513265119319</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+        <v>-0.9657751326511932</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YPR104C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FHL1</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -3267,56 +3171,56 @@
         <v>0.3157950613264886</v>
       </c>
       <c r="G7">
-        <v>0.38262571412079638</v>
+        <v>0.3826257141207964</v>
       </c>
       <c r="H7">
-        <v>0.43581526313363472</v>
+        <v>0.4358152631336347</v>
       </c>
       <c r="I7">
         <v>0.4782773049276845</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YGL181W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GTS1</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>-3.2242922266377677E-2</v>
+        <v>-0.03224292226637768</v>
       </c>
       <c r="E8">
-        <v>-6.1751470781310151E-2</v>
+        <v>-0.06175147078131015</v>
       </c>
       <c r="F8">
-        <v>-8.8708089574238091E-2</v>
+        <v>-0.08870808957423809</v>
       </c>
       <c r="G8">
         <v>-0.11329146328094152</v>
       </c>
       <c r="H8">
-        <v>-0.13567501841380489</v>
+        <v>-0.1356750184138049</v>
       </c>
       <c r="I8">
         <v>-0.15602572213857252</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YOL089C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>HAL9</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>6.7845052971744368E-2</v>
+        <v>0.06784505297174437</v>
       </c>
       <c r="E9">
         <v>0.18862858665993665</v>
@@ -3328,18 +3232,18 @@
         <v>0.44416175642804434</v>
       </c>
       <c r="H9">
-        <v>0.54810033808210679</v>
+        <v>0.5481003380821068</v>
       </c>
       <c r="I9">
-        <v>0.63280748470854853</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+        <v>0.6328074847085485</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YGL073W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>HSF1</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -3357,88 +3261,88 @@
         <v>-0.8419727691483192</v>
       </c>
       <c r="H10">
-        <v>-0.98747875037930033</v>
+        <v>-0.9874787503793003</v>
       </c>
       <c r="I10">
         <v>-1.1091270004312481</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YMR021C</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MAC1</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0.33308470255701728</v>
+        <v>0.3330847025570173</v>
       </c>
       <c r="E11">
         <v>0.47346853390573274</v>
       </c>
       <c r="F11">
-        <v>0.53334057291150161</v>
+        <v>0.5333405729115016</v>
       </c>
       <c r="G11">
-        <v>0.55245880952970428</v>
+        <v>0.5524588095297043</v>
       </c>
       <c r="H11">
-        <v>0.54857190869014838</v>
+        <v>0.5485719086901484</v>
       </c>
       <c r="I11">
-        <v>0.53080304375720466</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
+        <v>0.5308030437572047</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YOL116W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MSN1</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0.23856485325887899</v>
+        <v>0.238564853258879</v>
       </c>
       <c r="E12">
-        <v>3.3790313068777222E-2</v>
+        <v>0.03379031306877722</v>
       </c>
       <c r="F12">
-        <v>-0.20210744561253691</v>
+        <v>-0.2021074456125369</v>
       </c>
       <c r="G12">
-        <v>-0.39907999927305382</v>
+        <v>-0.3990799992730538</v>
       </c>
       <c r="H12">
-        <v>-0.55134245790464442</v>
+        <v>-0.5513424579046444</v>
       </c>
       <c r="I12">
-        <v>-0.67170289728681509</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+        <v>-0.6717028972868151</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MSN4</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0.69683618225821919</v>
+        <v>0.6968361822582192</v>
       </c>
       <c r="E13">
-        <v>0.99605147147935524</v>
+        <v>0.9960514714793552</v>
       </c>
       <c r="F13">
-        <v>1.1595868266004881</v>
+        <v>1.159586826600488</v>
       </c>
       <c r="G13">
         <v>1.2614316487437733</v>
@@ -3450,12 +3354,12 @@
         <v>1.3835586736624141</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YDR043C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>NRG1</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -3467,39 +3371,39 @@
         <v>-0.528092391912663</v>
       </c>
       <c r="F14">
-        <v>-0.54535498301068908</v>
+        <v>-0.5453549830106891</v>
       </c>
       <c r="G14">
         <v>-0.48481830187229835</v>
       </c>
       <c r="H14">
-        <v>-0.40689018918190362</v>
+        <v>-0.4068901891819036</v>
       </c>
       <c r="I14">
         <v>-0.33564151951966104</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL043W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0.37675704638511409</v>
+        <v>0.3767570463851141</v>
       </c>
       <c r="E15">
-        <v>0.50941477351297815</v>
+        <v>0.5094147735129781</v>
       </c>
       <c r="F15">
         <v>0.542276123170922</v>
       </c>
       <c r="G15">
-        <v>0.52930012700485229</v>
+        <v>0.5293001270048523</v>
       </c>
       <c r="H15">
         <v>0.49607287371952935</v>
@@ -3508,18 +3412,18 @@
         <v>0.4559061818509218</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YNL216W</v>
+      </c>
+      <c r="B16" t="str">
+        <v>RAP1</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>-7.4597585725288698E-2</v>
+        <v>-0.0745975857252887</v>
       </c>
       <c r="E16">
         <v>-0.14101561042568297</v>
@@ -3528,7 +3432,7 @@
         <v>-0.19982809166228732</v>
       </c>
       <c r="G16">
-        <v>-0.25164285047054752</v>
+        <v>-0.2516428504705475</v>
       </c>
       <c r="H16">
         <v>-0.29708125814755554</v>
@@ -3537,12 +3441,12 @@
         <v>-0.33676065652788667</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YBR049C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>REB1</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3566,12 +3470,12 @@
         <v>-0.22864400253053718</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YPR065W</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ROX1</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -3583,24 +3487,24 @@
         <v>-0.38461538472273715</v>
       </c>
       <c r="F18">
-        <v>-0.57692307819797506</v>
+        <v>-0.5769230781979751</v>
       </c>
       <c r="G18">
-        <v>-0.76923077154777231</v>
+        <v>-0.7692307715477723</v>
       </c>
       <c r="H18">
         <v>-0.9615384610455926</v>
       </c>
       <c r="I18">
-        <v>-1.1538461530770181</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
+        <v>-1.153846153077018</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YER169W</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RPH1</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3624,12 +3528,12 @@
         <v>1.5459741716045703</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YHR206W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SKN7</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -3638,10 +3542,10 @@
         <v>0.3620470173202065</v>
       </c>
       <c r="E20">
-        <v>0.68841046023837882</v>
+        <v>0.6884104602383788</v>
       </c>
       <c r="F20">
-        <v>0.95110301324627211</v>
+        <v>0.9511030132462721</v>
       </c>
       <c r="G20">
         <v>1.155363101829342</v>
@@ -3653,12 +3557,12 @@
         <v>1.4351838541611563</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YML007W</v>
+      </c>
+      <c r="B21" t="str">
+        <v>YAP1</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3682,12 +3586,12 @@
         <v>1.492430872944583</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YDR259C</v>
+      </c>
+      <c r="B22" t="str">
+        <v>YAP6</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -3696,538 +3600,544 @@
         <v>-0.27905701103548847</v>
       </c>
       <c r="E22">
-        <v>-0.49356699498153611</v>
+        <v>-0.4935669949815361</v>
       </c>
       <c r="F22">
-        <v>-0.63742545118101712</v>
+        <v>-0.6374254511810171</v>
       </c>
       <c r="G22">
-        <v>-0.71479591301793532</v>
+        <v>-0.7147959130179353</v>
       </c>
       <c r="H22">
-        <v>-0.73819673883883463</v>
+        <v>-0.7381967388388346</v>
       </c>
       <c r="I22">
-        <v>-0.72354373041145814</v>
+        <v>-0.7235437304114581</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I22"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>DegradationRate</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YKL112W</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ABF1</v>
       </c>
       <c r="C2">
         <v>0.34657359027997264</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ACE2</v>
       </c>
       <c r="C3">
         <v>0.23104906018664842</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YGL071W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AFT1</v>
       </c>
       <c r="C4">
-        <v>3.0136833937388925E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+        <v>0.030136833937388925</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="C5">
-        <v>2.7179999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+        <v>0.02718</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YPL177C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CUP9</v>
       </c>
       <c r="C6">
-        <v>2.5672117798516494E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+        <v>0.025672117798516494</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YPR104C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FHL1</v>
       </c>
       <c r="C7">
-        <v>1.7328679513998631E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>0.01732867951399863</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YGL181W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GTS1</v>
       </c>
       <c r="C8">
-        <v>1.1002336199364211E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
+        <v>0.01100233619936421</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YOL089C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>HAL9</v>
       </c>
       <c r="C9">
-        <v>2.7179999999999999E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+        <v>0.02718</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YGL073W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>HSF1</v>
       </c>
       <c r="C10">
-        <v>2.7179999999999999E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
+        <v>0.02718</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YMR021C</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MAC1</v>
       </c>
       <c r="C11">
-        <v>7.453195489891885E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
+        <v>0.007453195489891885</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YOL116W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MSN1</v>
       </c>
       <c r="C12">
-        <v>7.7016353395549478E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+        <v>0.07701635339554948</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MSN4</v>
       </c>
       <c r="C13">
-        <v>2.7179999999999999E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
+        <v>0.02718</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YDR043C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>NRG1</v>
       </c>
       <c r="C14">
-        <v>6.9314718055994526E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
+        <v>0.06931471805599453</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL043W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="C15">
-        <v>4.9510512897138946E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
+        <v>0.049510512897138946</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YNL216W</v>
+      </c>
+      <c r="B16" t="str">
+        <v>RAP1</v>
       </c>
       <c r="C16">
-        <v>1.6503504299046318E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>0.016503504299046318</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YBR049C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>REB1</v>
       </c>
       <c r="C17">
-        <v>5.7762265046662105E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+        <v>0.057762265046662105</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YPR065W</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ROX1</v>
       </c>
       <c r="C18">
-        <v>1.332975347230664E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
+        <v>0.01332975347230664</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YER169W</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RPH1</v>
       </c>
       <c r="C19">
-        <v>1.2602676010180823E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
+        <v>0.012602676010180823</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YHR206W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SKN7</v>
       </c>
       <c r="C20">
-        <v>3.0136833937388925E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
+        <v>0.030136833937388925</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YML007W</v>
+      </c>
+      <c r="B21" t="str">
+        <v>YAP1</v>
       </c>
       <c r="C21">
-        <v>3.0136833937388925E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
+        <v>0.030136833937388925</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YDR259C</v>
+      </c>
+      <c r="B22" t="str">
+        <v>YAP6</v>
       </c>
       <c r="C22">
-        <v>3.3007008598092635E-2</v>
+        <v>0.033007008598092635</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>SystematicName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>StandardName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>production_rates</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>YKL112W</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ABF1</v>
       </c>
       <c r="C2">
         <v>1.4647501152208167</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>YLR131C</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ACE2</v>
       </c>
       <c r="C3">
-        <v>0.61756754310209183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>0.6175675431020918</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>YGL071W</v>
+      </c>
+      <c r="B4" t="str">
+        <v>AFT1</v>
       </c>
       <c r="C4">
         <v>0.13213618203605254</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>YOR028C</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="C5">
         <v>0.17183551724098942</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>YPL177C</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CUP9</v>
       </c>
       <c r="C6">
         <v>0.13857337954030421</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>YPR104C</v>
+      </c>
+      <c r="B7" t="str">
+        <v>FHL1</v>
       </c>
       <c r="C7">
-        <v>9.5573071327759274E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>0.09557307132775927</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>YGL181W</v>
+      </c>
+      <c r="B8" t="str">
+        <v>GTS1</v>
       </c>
       <c r="C8">
-        <v>1.733680952262396E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
+        <v>0.01733680952262396</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>YOL089C</v>
+      </c>
+      <c r="B9" t="str">
+        <v>HAL9</v>
       </c>
       <c r="C9">
-        <v>0.63931909300407519</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+        <v>0.6393190930040752</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>YGL073W</v>
+      </c>
+      <c r="B10" t="str">
+        <v>HSF1</v>
       </c>
       <c r="C10">
-        <v>1.8101470219449828E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
+        <v>0.018101470219449828</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>YMR021C</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MAC1</v>
       </c>
       <c r="C11">
-        <v>0.48527141821372932</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
+        <v>0.4852714182137293</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>YOL116W</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MSN1</v>
       </c>
       <c r="C12">
         <v>0.5895545931776961</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>YKL062W</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MSN4</v>
       </c>
       <c r="C13">
-        <v>0.32714212674574389</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
+        <v>0.3271421267457439</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>YDR043C</v>
+      </c>
+      <c r="B14" t="str">
+        <v>NRG1</v>
       </c>
       <c r="C14">
-        <v>0.68230335258444386</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
+        <v>0.6823033525844439</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>YKL043W</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="C15">
         <v>0.2727248267444915</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>YNL216W</v>
+      </c>
+      <c r="B16" t="str">
+        <v>RAP1</v>
       </c>
       <c r="C16">
-        <v>2.2073873696625564E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>0.022073873696625564</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>YBR049C</v>
+      </c>
+      <c r="B17" t="str">
+        <v>REB1</v>
       </c>
       <c r="C17">
-        <v>8.2307397934961876E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+        <v>0.08230739793496188</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>YPR065W</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ROX1</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>YER169W</v>
+      </c>
+      <c r="B19" t="str">
+        <v>RPH1</v>
       </c>
       <c r="C19">
-        <v>0.89143565346094111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
+        <v>0.8914356534609411</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>YHR206W</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SKN7</v>
       </c>
       <c r="C20">
         <v>0.38930512637749964</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YML007W</v>
+      </c>
+      <c r="B21" t="str">
+        <v>YAP1</v>
       </c>
       <c r="C21">
-        <v>0.79398782516712441</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
+        <v>0.7939878251671244</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YDR259C</v>
+      </c>
+      <c r="B22" t="str">
+        <v>YAP6</v>
       </c>
       <c r="C22">
-        <v>9.1202898189687853E-2</v>
+        <v>0.09120289818968785</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>46</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>time</v>
       </c>
       <c r="B1">
         <v>15</v>
@@ -4241,85 +4151,87 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>cols regulators/rows targets</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ABF1</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ACE2</v>
+      </c>
+      <c r="D1" t="str">
+        <v>AFT1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>CIN5</v>
+      </c>
+      <c r="F1" t="str">
+        <v>CUP9</v>
+      </c>
+      <c r="G1" t="str">
+        <v>FHL1</v>
+      </c>
+      <c r="H1" t="str">
+        <v>GTS1</v>
+      </c>
+      <c r="I1" t="str">
+        <v>HAL9</v>
+      </c>
+      <c r="J1" t="str">
+        <v>HSF1</v>
+      </c>
+      <c r="K1" t="str">
+        <v>MAC1</v>
+      </c>
+      <c r="L1" t="str">
+        <v>MSN1</v>
+      </c>
+      <c r="M1" t="str">
+        <v>MSN4</v>
+      </c>
+      <c r="N1" t="str">
+        <v>NRG1</v>
+      </c>
+      <c r="O1" t="str">
+        <v>PHD1</v>
+      </c>
+      <c r="P1" t="str">
+        <v>RAP1</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>REB1</v>
+      </c>
+      <c r="R1" t="str">
+        <v>ROX1</v>
+      </c>
+      <c r="S1" t="str">
+        <v>RPH1</v>
+      </c>
+      <c r="T1" t="str">
+        <v>SKN7</v>
+      </c>
+      <c r="U1" t="str">
+        <v>YAP1</v>
+      </c>
+      <c r="V1" t="str">
+        <v>YAP6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ABF1</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -4385,9 +4297,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ACE2</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4453,9 +4365,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>AFT1</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4521,9 +4433,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CIN5</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4589,9 +4501,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CUP9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4657,9 +4569,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FHL1</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4725,9 +4637,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>15</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>GTS1</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -4793,9 +4705,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>17</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HAL9</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -4861,9 +4773,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HSF1</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -4929,9 +4841,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>21</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>MAC1</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -4997,9 +4909,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>23</v>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>MSN1</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -5065,9 +4977,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>25</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>MSN4</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -5133,9 +5045,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>27</v>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>NRG1</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -5201,9 +5113,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -5269,9 +5181,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>RAP1</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -5337,9 +5249,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>33</v>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>REB1</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -5405,9 +5317,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>35</v>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ROX1</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -5473,9 +5385,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>37</v>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>RPH1</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -5541,9 +5453,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>39</v>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SKN7</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5609,9 +5521,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>41</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YAP1</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -5677,9 +5589,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>43</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>YAP6</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5746,6 +5658,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:V22"/>
+  </ignoredErrors>
 </worksheet>
 </file>